--- a/03_DEP/a_non_imputed/c_data/06_pi_permutation.xlsx
+++ b/03_DEP/a_non_imputed/c_data/06_pi_permutation.xlsx
@@ -410,13 +410,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>105</v>
+        <v>105.15</v>
       </c>
       <c r="E2" t="n">
         <v>200</v>
@@ -433,10 +433,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="D3" t="n">
-        <v>109.1</v>
+        <v>111.15</v>
       </c>
       <c r="E3" t="n">
         <v>200</v>
@@ -450,19 +450,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>99.1</v>
+        <v>103</v>
       </c>
       <c r="E4" t="n">
         <v>200</v>
       </c>
       <c r="F4" t="n">
-        <v>0.218905472636816</v>
+        <v>0.223880597014925</v>
       </c>
     </row>
     <row r="5">
@@ -470,19 +470,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>106.1</v>
+        <v>110.15</v>
       </c>
       <c r="E5" t="n">
         <v>200</v>
       </c>
       <c r="F5" t="n">
-        <v>0.641791044776119</v>
+        <v>0.54726368159204</v>
       </c>
     </row>
     <row r="6">
@@ -490,19 +490,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" t="n">
-        <v>47</v>
+        <v>50.5</v>
       </c>
       <c r="D6" t="n">
-        <v>121.05</v>
+        <v>123.05</v>
       </c>
       <c r="E6" t="n">
         <v>200</v>
       </c>
       <c r="F6" t="n">
-        <v>0.915422885572139</v>
+        <v>0.925373134328358</v>
       </c>
     </row>
     <row r="7">
@@ -516,13 +516,13 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>71.05</v>
+        <v>72.1</v>
       </c>
       <c r="E7" t="n">
         <v>200</v>
       </c>
       <c r="F7" t="n">
-        <v>0.776119402985075</v>
+        <v>0.786069651741294</v>
       </c>
     </row>
     <row r="8">
@@ -530,19 +530,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="D8" t="n">
-        <v>77.05</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
         <v>200</v>
       </c>
       <c r="F8" t="n">
-        <v>0.472636815920398</v>
+        <v>0.477611940298507</v>
       </c>
     </row>
     <row r="9">
@@ -550,19 +550,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>77.5</v>
+        <v>78.5</v>
       </c>
       <c r="D9" t="n">
-        <v>161.1</v>
+        <v>161.15</v>
       </c>
       <c r="E9" t="n">
         <v>200</v>
       </c>
       <c r="F9" t="n">
-        <v>0.875621890547264</v>
+        <v>0.885572139303483</v>
       </c>
     </row>
     <row r="10">
@@ -570,13 +570,13 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="n">
-        <v>63.5</v>
+        <v>64</v>
       </c>
       <c r="D10" t="n">
-        <v>113.15</v>
+        <v>114.2</v>
       </c>
       <c r="E10" t="n">
         <v>200</v>
